--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203F4D72-F55B-4D43-8335-FDC5A33131C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9A9AD2-184A-4B2B-8C52-C5CFA1CB45D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>스테이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,23 +47,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돌 공장 X 3, 도로 X10, 새총 X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>궁수 X3, 화살공장 X 3, 도로 X5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총알 공장 X 3, 도로 X 5, 총 X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타워버프 X3, 공장 버프 X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">모든 공장 X3, 모든 방어 타워 X 2, </t>
+    <t>클리어골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌 공장 X 3, 새총 X3, 궁수 X3, 화살공장 X 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 공장 X 3, 도로 X 5, 총 X3, 공장 버프 X3, 타워버프 X3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -390,21 +386,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="28.875" customWidth="1"/>
-    <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="27.75" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="15.375" customWidth="1"/>
-    <col min="10" max="10" width="29.875" customWidth="1"/>
+    <col min="3" max="4" width="14.125" customWidth="1"/>
+    <col min="5" max="6" width="28.875" customWidth="1"/>
+    <col min="7" max="7" width="53" customWidth="1"/>
+    <col min="8" max="8" width="27.75" customWidth="1"/>
+    <col min="9" max="10" width="17.5" customWidth="1"/>
+    <col min="11" max="11" width="15.375" customWidth="1"/>
+    <col min="12" max="12" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -415,13 +411,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -429,16 +431,22 @@
         <v>150</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1000</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -446,16 +454,22 @@
         <v>200</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2000</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -463,54 +477,23 @@
         <v>300</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>500</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1000</v>
-      </c>
-      <c r="C6">
-        <v>0.8</v>
-      </c>
-      <c r="D6">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F9" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F12" s="1"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9A9AD2-184A-4B2B-8C52-C5CFA1CB45D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800862C0-3CB4-450F-A2AE-BCDE9BBA834B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800862C0-3CB4-450F-A2AE-BCDE9BBA834B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7431875-4A90-4E40-85AD-743615170094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>스테이지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,11 +55,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돌 공장 X 3, 새총 X3, 궁수 X3, 화살공장 X 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총알 공장 X 3, 도로 X 5, 총 X3, 공장 버프 X3, 타워버프 X3</t>
+    <t>돌 공장 X 2, 도로 X 4, 새총 X 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁수 X3, 화살공장 X 3, 도로 X 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 공장 X 3, 도로 X 15, 총 X1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장 버프 X3, 타워버프 X2, 총 X3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,19 +436,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>1</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -451,13 +459,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -474,19 +482,45 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>1500</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>500</v>
+      </c>
+      <c r="C5">
         <v>0.5</v>
       </c>
-      <c r="D4">
-        <v>12</v>
-      </c>
-      <c r="E4">
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>10</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7431875-4A90-4E40-85AD-743615170094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CB0230-CE37-422D-86A8-E4971FEFC756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -494,7 +494,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CB0230-CE37-422D-86A8-E4971FEFC756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8B9AD9-E13C-4249-8B92-3BA8FF4B38BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,16 +505,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>0</v>

--- a/Assets/0_Adventure/Deploy/스테이지.xlsx
+++ b/Assets/0_Adventure/Deploy/스테이지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8B9AD9-E13C-4249-8B92-3BA8FF4B38BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE2A218-6980-409A-8C59-7B7A7E0D7F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,10 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지을 수 있는 건물(기본으로 1을 지을 수 있고, 깨면 다음 스테이지의 건물이 추가됨)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>클리어골드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -68,6 +64,10 @@
   </si>
   <si>
     <t>공장 버프 X3, 타워버프 X2, 총 X3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지을 수 있는 건물(기본으로 1을 지을 수 있고, 깨면 건물이 추가됨)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -419,16 +419,16 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -451,7 +451,7 @@
         <v>1200</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -474,7 +474,7 @@
         <v>3000</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -497,7 +497,7 @@
         <v>5000</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
